--- a/master/result/96_重生逆袭_从零开始/96_重生逆袭_从零开始.xlsx
+++ b/master/result/96_重生逆袭_从零开始/96_重生逆袭_从零开始.xlsx
@@ -397,467 +397,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D41"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>yard</v>
       </c>
       <c r="B2" t="str">
-        <v>yard</v>
+        <v>/yard/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>院子</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>bill</v>
       </c>
       <c r="B3" t="str">
-        <v>bill</v>
+        <v>/bill/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>账单</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>brochure</v>
       </c>
       <c r="B4" t="str">
-        <v>brochure</v>
+        <v>/brochure/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>小册子</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>engineer</v>
       </c>
       <c r="B5" t="str">
-        <v>engineer</v>
+        <v>/engineer/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>工程师</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>skillful</v>
       </c>
       <c r="B6" t="str">
+        <v>/skillful/</v>
+      </c>
+      <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>娴熟的</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>actress</v>
+      </c>
+      <c r="B7" t="str">
+        <v>/actress/</v>
+      </c>
+      <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>女演员</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>presently</v>
+      </c>
+      <c r="B8" t="str">
+        <v>/presently/</v>
+      </c>
+      <c r="C8" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>不久</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>handsome</v>
+      </c>
+      <c r="B9" t="str">
+        <v>/handsome/</v>
+      </c>
+      <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>漂亮的</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>drill</v>
+      </c>
+      <c r="B10" t="str">
+        <v>/drill/</v>
+      </c>
+      <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>练习</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>analytic</v>
+      </c>
+      <c r="B11" t="str">
+        <v>/analytic/</v>
+      </c>
+      <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>分析的</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>chance</v>
+      </c>
+      <c r="B12" t="str">
+        <v>/chance/</v>
+      </c>
+      <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>机会</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>quit</v>
+      </c>
+      <c r="B13" t="str">
+        <v>/kwɪt/</v>
+      </c>
+      <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>放弃</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>other</v>
+      </c>
+      <c r="B14" t="str">
+        <v>/other/</v>
+      </c>
+      <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>其他</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>figure</v>
+      </c>
+      <c r="B15" t="str">
+        <v>/figure/</v>
+      </c>
+      <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>数字</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>campaign</v>
+      </c>
+      <c r="B16" t="str">
+        <v>/kæmˈpeɪn/</v>
+      </c>
+      <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>运动</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>empirical</v>
+      </c>
+      <c r="B17" t="str">
+        <v>/empirical/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>经验的</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>stake</v>
+      </c>
+      <c r="B18" t="str">
+        <v>/stake/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>赌注</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>compartment</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/compartment/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>隔间</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>watch</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/wɒtʃ/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>观看</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>update</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/ʌpˈdeɪt/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>更新</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>guideline</v>
+      </c>
+      <c r="B22" t="str">
+        <v>/guideline/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>指导方针</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
         <v>skillful</v>
       </c>
-      <c r="C6" t="str">
-        <v>娴熟的</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>actress</v>
-      </c>
-      <c r="C7" t="str">
-        <v>女演员</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>presently</v>
-      </c>
-      <c r="C8" t="str">
-        <v>不久</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>handsome</v>
-      </c>
-      <c r="C9" t="str">
-        <v>漂亮的</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>drill</v>
-      </c>
-      <c r="C10" t="str">
-        <v>练习</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>analytic</v>
-      </c>
-      <c r="C11" t="str">
-        <v>分析的</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>chance</v>
-      </c>
-      <c r="C12" t="str">
-        <v>机会</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>quit</v>
-      </c>
-      <c r="C13" t="str">
-        <v>放弃</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>other</v>
-      </c>
-      <c r="C14" t="str">
-        <v>其他</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>figure</v>
-      </c>
-      <c r="C15" t="str">
-        <v>数字</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>campaign</v>
-      </c>
-      <c r="C16" t="str">
-        <v>运动</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>empirical</v>
-      </c>
-      <c r="C17" t="str">
-        <v>经验的</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>stake</v>
-      </c>
-      <c r="C18" t="str">
-        <v>赌注</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>compartment</v>
-      </c>
-      <c r="C19" t="str">
-        <v>隔间</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>watch</v>
-      </c>
-      <c r="C20" t="str">
-        <v>观看</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>update</v>
-      </c>
-      <c r="C21" t="str">
-        <v>更新</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>guideline</v>
-      </c>
-      <c r="C22" t="str">
-        <v>指导方针</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
       <c r="B23" t="str">
-        <v>skillful</v>
+        <v>/skillful/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>娴熟</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>transparent</v>
       </c>
       <c r="B24" t="str">
-        <v>transparent</v>
+        <v>/transparent/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>透明</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>afford</v>
       </c>
       <c r="B25" t="str">
-        <v>afford</v>
+        <v>/əˈfɔːd/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>担负</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>household</v>
       </c>
       <c r="B26" t="str">
-        <v>household</v>
+        <v>/household/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>家庭</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>relief</v>
       </c>
       <c r="B27" t="str">
-        <v>relief</v>
+        <v>/relief/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>解脱</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>setting</v>
       </c>
       <c r="B28" t="str">
-        <v>setting</v>
+        <v>/setting/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>环境</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>scope</v>
       </c>
       <c r="B29" t="str">
-        <v>scope</v>
+        <v>/scope/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>范围</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>cling</v>
       </c>
       <c r="B30" t="str">
-        <v>cling</v>
+        <v>/cling/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>坚持</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>health</v>
       </c>
       <c r="B31" t="str">
-        <v>health</v>
+        <v>/health/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>健康</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>generator</v>
       </c>
       <c r="B32" t="str">
-        <v>generator</v>
+        <v>/generator/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>发电机</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>medieval</v>
       </c>
       <c r="B33" t="str">
-        <v>medieval</v>
+        <v>/medieval/</v>
       </c>
       <c r="C33" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>中世纪</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>weld</v>
       </c>
       <c r="B34" t="str">
-        <v>weld</v>
+        <v>/weld/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>焊接</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>leaf</v>
       </c>
       <c r="B35" t="str">
-        <v>leaf</v>
+        <v>/leaf/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>叶子</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>steak</v>
       </c>
       <c r="B36" t="str">
-        <v>steak</v>
+        <v>/steak/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>牛排</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>ham</v>
       </c>
       <c r="B37" t="str">
-        <v>ham</v>
+        <v>/ham/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>火腿</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>consequently</v>
       </c>
       <c r="B38" t="str">
-        <v>consequently</v>
+        <v>/ˈkɒnsɪkwəntli/</v>
       </c>
       <c r="C38" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D38" t="str">
         <v>因此</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>entry</v>
       </c>
       <c r="B39" t="str">
-        <v>entry</v>
+        <v>/entry/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>入口</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>it</v>
       </c>
       <c r="B40" t="str">
-        <v>it</v>
+        <v>/it/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>它</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>lest</v>
       </c>
       <c r="B41" t="str">
-        <v>lest</v>
+        <v>/lest/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>免得</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
   </ignoredErrors>
 </worksheet>
 </file>